--- a/Incubesa - costo por lote.xlsx
+++ b/Incubesa - costo por lote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\modelos\ETL_SIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D170BA-F4F0-4E46-83C3-BD75FD3FF35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0024B0BA-00C4-41B6-8217-2E294C971DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{16796DCF-AB18-4F61-91BE-3563DA027DA6}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="75">
   <si>
     <t xml:space="preserve"> AMORTIZACIONES</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>DEPRECIACIONES</t>
+  </si>
+  <si>
+    <t>SIN INF</t>
   </si>
 </sst>
 </file>
@@ -889,6 +892,9 @@
       <c r="B2" s="15" t="s">
         <v>34</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D2" s="9">
         <v>2977349</v>
       </c>
@@ -990,6 +996,9 @@
       <c r="B3" s="15" t="s">
         <v>34</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D3" s="9">
         <v>2702573</v>
       </c>
@@ -1091,6 +1100,9 @@
       <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D4" s="9">
         <v>3275700</v>
       </c>
@@ -1192,6 +1204,9 @@
       <c r="B5" s="15" t="s">
         <v>34</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D5" s="9">
         <v>3217675</v>
       </c>
@@ -1292,6 +1307,9 @@
       </c>
       <c r="B6" s="15" t="s">
         <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D6" s="9">
         <v>2822337</v>

--- a/Incubesa - costo por lote.xlsx
+++ b/Incubesa - costo por lote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\modelos\ETL_SIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0024B0BA-00C4-41B6-8217-2E294C971DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89965C6C-2B30-413D-AD0A-A6B104DD64FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{16796DCF-AB18-4F61-91BE-3563DA027DA6}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="104">
   <si>
     <t xml:space="preserve"> AMORTIZACIONES</t>
   </si>
@@ -282,7 +282,94 @@
     <t>DEPRECIACIONES</t>
   </si>
   <si>
-    <t>SIN INF</t>
+    <t>AH-2125</t>
+  </si>
+  <si>
+    <t>AH-2225</t>
+  </si>
+  <si>
+    <t>AH-2325</t>
+  </si>
+  <si>
+    <t>AH-2425</t>
+  </si>
+  <si>
+    <t>AH-2525</t>
+  </si>
+  <si>
+    <t>AH-2625</t>
+  </si>
+  <si>
+    <t>AH-2725</t>
+  </si>
+  <si>
+    <t>ESP-055</t>
+  </si>
+  <si>
+    <t>ESP-176</t>
+  </si>
+  <si>
+    <t>ESP-177</t>
+  </si>
+  <si>
+    <t>LMA-580</t>
+  </si>
+  <si>
+    <t>SC1-2825</t>
+  </si>
+  <si>
+    <t>SC1-2925</t>
+  </si>
+  <si>
+    <t>SC1-3025</t>
+  </si>
+  <si>
+    <t>SC1-3125</t>
+  </si>
+  <si>
+    <t>SC1-3225</t>
+  </si>
+  <si>
+    <t>SC1-3325</t>
+  </si>
+  <si>
+    <t>SC1-3425</t>
+  </si>
+  <si>
+    <t>SEL-174</t>
+  </si>
+  <si>
+    <t>SEL-175</t>
+  </si>
+  <si>
+    <t>SEL-581</t>
+  </si>
+  <si>
+    <t>SRU-179</t>
+  </si>
+  <si>
+    <t>TO-1425</t>
+  </si>
+  <si>
+    <t>TO-1525</t>
+  </si>
+  <si>
+    <t>TO-1625</t>
+  </si>
+  <si>
+    <t>TO-1725</t>
+  </si>
+  <si>
+    <t>VIC-053</t>
+  </si>
+  <si>
+    <t>VIC-054</t>
+  </si>
+  <si>
+    <t>VIL-178</t>
+  </si>
+  <si>
+    <t>VIL-582</t>
   </si>
 </sst>
 </file>
@@ -775,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA9DC54-BF76-4DB6-861F-C807799E45EB}">
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="11.5703125" style="1"/>
@@ -887,7 +974,7 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
-        <v>46053</v>
+        <v>46203</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>34</v>
@@ -896,46 +983,46 @@
         <v>74</v>
       </c>
       <c r="D2" s="9">
-        <v>2977349</v>
+        <v>37469</v>
       </c>
       <c r="E2" s="10">
-        <v>2284833</v>
+        <v>20287</v>
       </c>
       <c r="F2" s="11">
-        <v>0.76740516479593091</v>
+        <v>0.54143425231524722</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
       <c r="H2" s="13">
-        <v>297.90000000000003</v>
+        <v>3.3426189098821677</v>
       </c>
       <c r="I2" s="14">
-        <v>1024951.4700000008</v>
+        <v>11043.98</v>
       </c>
       <c r="J2" s="14">
-        <v>0</v>
+        <v>21.802662436989603</v>
       </c>
       <c r="K2" s="9">
-        <v>0</v>
+        <v>1.1935924690769439</v>
       </c>
       <c r="L2" s="9">
-        <v>1876.15</v>
+        <v>14.89782600277378</v>
       </c>
       <c r="M2" s="14">
-        <v>0</v>
+        <v>5.2703667468357276</v>
       </c>
       <c r="N2" s="10">
-        <v>18875.170000000002</v>
+        <v>161.48098114232826</v>
       </c>
       <c r="O2" s="14">
-        <v>6481.81</v>
+        <v>132.63348315444156</v>
       </c>
       <c r="P2" s="14">
         <v>0</v>
       </c>
       <c r="Q2" s="14">
-        <v>0</v>
+        <v>1.8399883906682108</v>
       </c>
       <c r="R2" s="14">
         <v>0</v>
@@ -944,46 +1031,46 @@
         <v>0</v>
       </c>
       <c r="T2" s="14">
-        <v>1850.4</v>
+        <v>13.174556875670129</v>
       </c>
       <c r="U2" s="14">
-        <v>307.44</v>
+        <v>15.07550488171613</v>
       </c>
       <c r="V2" s="14">
-        <v>0</v>
+        <v>79.462458634854571</v>
       </c>
       <c r="W2" s="14">
-        <v>4662.91</v>
+        <v>142.10374340222037</v>
       </c>
       <c r="X2" s="14">
-        <v>50156.979999999996</v>
+        <v>312.63178746247382</v>
       </c>
       <c r="Y2" s="14">
-        <v>0</v>
+        <v>14.941825725159324</v>
       </c>
       <c r="Z2" s="14">
-        <v>0</v>
+        <v>83.059235941134688</v>
       </c>
       <c r="AA2" s="14">
-        <v>0</v>
+        <v>11.018010482311739</v>
       </c>
       <c r="AB2" s="14">
-        <v>0</v>
+        <v>2.0010273745993028</v>
       </c>
       <c r="AC2" s="14">
-        <v>0</v>
+        <v>4.612850895405205</v>
       </c>
       <c r="AD2" s="14">
-        <v>6580.66</v>
+        <v>66.640779532716508</v>
       </c>
       <c r="AE2" s="14">
-        <v>56508.560000000012</v>
+        <v>448.39797085127088</v>
       </c>
       <c r="AF2" s="14">
-        <v>0</v>
+        <v>72.535302341464984</v>
       </c>
       <c r="AG2" s="14">
-        <v>11582.050000000001</v>
+        <v>100.06424864870623</v>
       </c>
       <c r="AH2" s="14">
         <v>0</v>
@@ -991,55 +1078,55 @@
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
-        <v>46081</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="9">
-        <v>2702573</v>
+        <v>39390</v>
       </c>
       <c r="E3" s="10">
-        <v>2011447</v>
+        <v>26752</v>
       </c>
       <c r="F3" s="11">
-        <v>0.74427110757045234</v>
+        <v>0.67915714648387915</v>
       </c>
       <c r="G3" s="13">
         <v>0</v>
       </c>
       <c r="H3" s="13">
-        <v>525.03</v>
+        <v>4.4078346269614901</v>
       </c>
       <c r="I3" s="14">
-        <v>909058.38999999955</v>
+        <v>11611.120000000004</v>
       </c>
       <c r="J3" s="14">
-        <v>0</v>
+        <v>28.750669173083544</v>
       </c>
       <c r="K3" s="9">
-        <v>0</v>
+        <v>1.5739629187532116</v>
       </c>
       <c r="L3" s="9">
-        <v>1876.15</v>
+        <v>19.645420280288075</v>
       </c>
       <c r="M3" s="14">
-        <v>0</v>
+        <v>6.9499113329397835</v>
       </c>
       <c r="N3" s="10">
-        <v>13398.98</v>
+        <v>212.94125338983417</v>
       </c>
       <c r="O3" s="14">
-        <v>7852.14</v>
+        <v>174.90072171083062</v>
       </c>
       <c r="P3" s="14">
         <v>0</v>
       </c>
       <c r="Q3" s="14">
-        <v>0</v>
+        <v>2.4263503439225107</v>
       </c>
       <c r="R3" s="14">
         <v>0</v>
@@ -1048,46 +1135,46 @@
         <v>0</v>
       </c>
       <c r="T3" s="14">
-        <v>1824.8899999999999</v>
+        <v>17.37298494296482</v>
       </c>
       <c r="U3" s="14">
-        <v>3854.52</v>
+        <v>19.879721328716414</v>
       </c>
       <c r="V3" s="14">
-        <v>0</v>
+        <v>104.78531539407648</v>
       </c>
       <c r="W3" s="14">
-        <v>6823.24</v>
+        <v>187.38893594401338</v>
       </c>
       <c r="X3" s="14">
-        <v>72434.689999999988</v>
+        <v>412.2603429879282</v>
       </c>
       <c r="Y3" s="14">
-        <v>0</v>
+        <v>19.703441701555786</v>
       </c>
       <c r="Z3" s="14">
-        <v>0</v>
+        <v>109.52830284897892</v>
       </c>
       <c r="AA3" s="14">
-        <v>0</v>
+        <v>14.529196846394422</v>
       </c>
       <c r="AB3" s="14">
-        <v>0</v>
+        <v>2.6387087457623375</v>
       </c>
       <c r="AC3" s="14">
-        <v>0</v>
+        <v>6.082860312213735</v>
       </c>
       <c r="AD3" s="14">
-        <v>2399.8300000000004</v>
+        <v>87.877662249678707</v>
       </c>
       <c r="AE3" s="14">
-        <v>63025.89</v>
+        <v>591.29208439952674</v>
       </c>
       <c r="AF3" s="14">
-        <v>0</v>
+        <v>95.650633816674286</v>
       </c>
       <c r="AG3" s="14">
-        <v>12060.379999999985</v>
+        <v>131.9524217405328</v>
       </c>
       <c r="AH3" s="14">
         <v>0</v>
@@ -1095,55 +1182,55 @@
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="9">
-        <v>3275700</v>
+        <v>44861</v>
       </c>
       <c r="E4" s="10">
-        <v>2572413</v>
+        <v>38492</v>
       </c>
       <c r="F4" s="11">
-        <v>0.78530176756113201</v>
+        <v>0.858028131339025</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
       </c>
       <c r="H4" s="13">
-        <v>257.87</v>
+        <v>6.3421938718974911</v>
       </c>
       <c r="I4" s="14">
-        <v>1090390.0100000005</v>
+        <v>13215.210000000001</v>
       </c>
       <c r="J4" s="14">
-        <v>0</v>
+        <v>41.3677765329819</v>
       </c>
       <c r="K4" s="9">
-        <v>0</v>
+        <v>2.2646897678173077</v>
       </c>
       <c r="L4" s="9">
-        <v>1876.15</v>
+        <v>28.266728372788897</v>
       </c>
       <c r="M4" s="14">
-        <v>0</v>
+        <v>9.9998499935525622</v>
       </c>
       <c r="N4" s="10">
-        <v>20109.29</v>
+        <v>306.38960546805833</v>
       </c>
       <c r="O4" s="14">
-        <v>13184.69</v>
+        <v>251.65515027262606</v>
       </c>
       <c r="P4" s="14">
         <v>0</v>
       </c>
       <c r="Q4" s="14">
-        <v>0</v>
+        <v>3.4911437439542943</v>
       </c>
       <c r="R4" s="14">
         <v>0</v>
@@ -1152,46 +1239,46 @@
         <v>0</v>
       </c>
       <c r="T4" s="14">
-        <v>1646.83</v>
+        <v>24.997044573288047</v>
       </c>
       <c r="U4" s="14">
-        <v>8901.5400000000009</v>
+        <v>28.603851427368131</v>
       </c>
       <c r="V4" s="14">
-        <v>0</v>
+        <v>150.76989982613605</v>
       </c>
       <c r="W4" s="14">
-        <v>11126.46</v>
+        <v>269.62376354504198</v>
       </c>
       <c r="X4" s="14">
-        <v>63565.880000000012</v>
+        <v>593.17901922440683</v>
       </c>
       <c r="Y4" s="14">
-        <v>0</v>
+        <v>28.350212244926933</v>
       </c>
       <c r="Z4" s="14">
-        <v>10874.34</v>
+        <v>157.59432690127454</v>
       </c>
       <c r="AA4" s="14">
-        <v>0</v>
+        <v>20.90527231651518</v>
       </c>
       <c r="AB4" s="14">
-        <v>0</v>
+        <v>3.7966947159795117</v>
       </c>
       <c r="AC4" s="14">
-        <v>0</v>
+        <v>8.7522973660934174</v>
       </c>
       <c r="AD4" s="14">
-        <v>5932.03</v>
+        <v>126.44239590739507</v>
       </c>
       <c r="AE4" s="14">
-        <v>67410.63</v>
+        <v>850.77806940440269</v>
       </c>
       <c r="AF4" s="14">
-        <v>0</v>
+        <v>137.62650257444031</v>
       </c>
       <c r="AG4" s="14">
-        <v>11899.289999999995</v>
+        <v>189.85917380519544</v>
       </c>
       <c r="AH4" s="14">
         <v>0</v>
@@ -1199,55 +1286,55 @@
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9">
-        <v>3217675</v>
+        <v>7177</v>
       </c>
       <c r="E5" s="10">
-        <v>2527475</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="11">
-        <v>0.78549729229956411</v>
+        <v>0.69666991779294973</v>
       </c>
       <c r="G5" s="13">
         <v>0</v>
       </c>
       <c r="H5" s="13">
-        <v>360.27</v>
+        <v>0.8238327278262354</v>
       </c>
       <c r="I5" s="14">
-        <v>1074135.5100000005</v>
+        <v>2472.15</v>
       </c>
       <c r="J5" s="14">
-        <v>0</v>
+        <v>5.3735550936534731</v>
       </c>
       <c r="K5" s="9">
-        <v>0</v>
+        <v>0.29417668188419771</v>
       </c>
       <c r="L5" s="9">
-        <v>1876.15</v>
+        <v>3.6717666492763295</v>
       </c>
       <c r="M5" s="14">
-        <v>0</v>
+        <v>1.2989517293921546</v>
       </c>
       <c r="N5" s="10">
-        <v>20281.89</v>
+        <v>39.799127801628693</v>
       </c>
       <c r="O5" s="14">
-        <v>13777.27</v>
+        <v>32.689279625977612</v>
       </c>
       <c r="P5" s="14">
         <v>0</v>
       </c>
       <c r="Q5" s="14">
-        <v>0</v>
+        <v>0.45348952301183293</v>
       </c>
       <c r="R5" s="14">
         <v>0</v>
@@ -1256,46 +1343,46 @@
         <v>0</v>
       </c>
       <c r="T5" s="14">
-        <v>80.78</v>
+        <v>3.2470441355720729</v>
       </c>
       <c r="U5" s="14">
-        <v>3489.4300000000003</v>
+        <v>3.7155579636506459</v>
       </c>
       <c r="V5" s="14">
-        <v>0</v>
+        <v>19.584575993211065</v>
       </c>
       <c r="W5" s="14">
-        <v>18273.48</v>
+        <v>35.023350767047958</v>
       </c>
       <c r="X5" s="14">
-        <v>51947.37</v>
+        <v>77.052247119454279</v>
       </c>
       <c r="Y5" s="14">
-        <v>0</v>
+        <v>3.682610963957047</v>
       </c>
       <c r="Z5" s="14">
-        <v>10567.16</v>
+        <v>20.471049426020283</v>
       </c>
       <c r="AA5" s="14">
-        <v>0</v>
+        <v>2.7155346976664214</v>
       </c>
       <c r="AB5" s="14">
-        <v>0</v>
+        <v>0.49317971474325989</v>
       </c>
       <c r="AC5" s="14">
-        <v>0</v>
+        <v>1.1368982341906653</v>
       </c>
       <c r="AD5" s="14">
-        <v>5339.37</v>
+        <v>16.424503261378348</v>
       </c>
       <c r="AE5" s="14">
-        <v>55877.350000000006</v>
+        <v>110.51362223376321</v>
       </c>
       <c r="AF5" s="14">
-        <v>0</v>
+        <v>17.877286523750428</v>
       </c>
       <c r="AG5" s="14">
-        <v>13028.320000000032</v>
+        <v>24.662160163825657</v>
       </c>
       <c r="AH5" s="14">
         <v>0</v>
@@ -1303,900 +1390,3123 @@
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D6" s="9">
-        <v>2822337</v>
+        <v>242094</v>
       </c>
       <c r="E6" s="10">
-        <v>2171540</v>
+        <v>161100</v>
       </c>
       <c r="F6" s="11">
-        <v>0.76941201564519046</v>
-      </c>
-      <c r="G6" s="13"/>
+        <v>0.66544400109048552</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0</v>
+      </c>
       <c r="H6" s="13">
-        <v>360.27</v>
+        <v>26.543890490561306</v>
       </c>
       <c r="I6" s="14">
-        <v>963501.98</v>
+        <v>85572.36</v>
       </c>
       <c r="J6" s="14">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9"/>
+        <v>173.13594511751489</v>
+      </c>
+      <c r="K6" s="9">
+        <v>9.4783726903088503</v>
+      </c>
       <c r="L6" s="9">
-        <v>1870.19</v>
-      </c>
-      <c r="M6" s="14"/>
+        <v>118.30432143968333</v>
+      </c>
+      <c r="M6" s="14">
+        <v>41.852224721015219</v>
+      </c>
       <c r="N6" s="10">
-        <v>19000</v>
+        <v>1282.3278977684765</v>
       </c>
       <c r="O6" s="14">
-        <v>14138.77</v>
-      </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
+        <v>1053.2485895489988</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>14.611432431441257</v>
+      </c>
+      <c r="R6" s="14">
+        <v>0</v>
+      </c>
+      <c r="S6" s="14">
+        <v>0</v>
+      </c>
       <c r="T6" s="14">
-        <v>80.78</v>
+        <v>104.61976204813219</v>
       </c>
       <c r="U6" s="14">
-        <v>6996.02</v>
-      </c>
-      <c r="V6" s="14"/>
+        <v>119.71527758882381</v>
+      </c>
+      <c r="V6" s="14">
+        <v>631.01503850126051</v>
+      </c>
       <c r="W6" s="14">
-        <v>10933.01</v>
+        <v>1128.4523617142852</v>
       </c>
       <c r="X6" s="14">
-        <v>65529.760000000017</v>
-      </c>
-      <c r="Y6" s="14"/>
+        <v>2482.6234021888167</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>118.65372525869606</v>
+      </c>
       <c r="Z6" s="14">
-        <v>9862.11</v>
-      </c>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
+        <v>659.57721250637348</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>87.4945279588121</v>
+      </c>
+      <c r="AB6" s="14">
+        <v>15.890250409027834</v>
+      </c>
+      <c r="AC6" s="14">
+        <v>36.630861105623232</v>
+      </c>
       <c r="AD6" s="14">
-        <v>8927.2900000000009</v>
+        <v>529.19749508161033</v>
       </c>
       <c r="AE6" s="14">
-        <v>56852.580000000009</v>
-      </c>
-      <c r="AF6" s="14"/>
+        <v>3560.7489083718506</v>
+      </c>
+      <c r="AF6" s="14">
+        <v>576.00617179523874</v>
+      </c>
       <c r="AG6" s="14">
-        <v>12373.910000000016</v>
-      </c>
-      <c r="AH6" s="14"/>
+        <v>794.61480047846271</v>
+      </c>
+      <c r="AH6" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="15"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
-      <c r="AF7" s="14"/>
-      <c r="AG7" s="14"/>
-      <c r="AH7" s="14"/>
+      <c r="A7" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="9">
+        <v>195612</v>
+      </c>
+      <c r="E7" s="10">
+        <v>156912</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.80215937672535431</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>25.853848197734052</v>
+      </c>
+      <c r="I7" s="14">
+        <v>68652.529999999984</v>
+      </c>
+      <c r="J7" s="14">
+        <v>168.63505537107076</v>
+      </c>
+      <c r="K7" s="9">
+        <v>9.2319703015626473</v>
+      </c>
+      <c r="L7" s="9">
+        <v>115.22884969424949</v>
+      </c>
+      <c r="M7" s="14">
+        <v>40.76422275247635</v>
+      </c>
+      <c r="N7" s="12">
+        <v>1248.9921483218325</v>
+      </c>
+      <c r="O7" s="14">
+        <v>1025.8680489342798</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>14.231589606966544</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
+      </c>
+      <c r="S7" s="14">
+        <v>0</v>
+      </c>
+      <c r="T7" s="14">
+        <v>101.90003788017702</v>
+      </c>
+      <c r="U7" s="14">
+        <v>116.60312623847003</v>
+      </c>
+      <c r="V7" s="14">
+        <v>614.61099764934693</v>
+      </c>
+      <c r="W7" s="14">
+        <v>1099.1168031118059</v>
+      </c>
+      <c r="X7" s="14">
+        <v>2418.0844400015621</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>115.56917031528563</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>642.43066150713889</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>85.2199960960467</v>
+      </c>
+      <c r="AB7" s="14">
+        <v>15.47716307995888</v>
+      </c>
+      <c r="AC7" s="14">
+        <v>35.678595144665131</v>
+      </c>
+      <c r="AD7" s="14">
+        <v>515.44033114987985</v>
+      </c>
+      <c r="AE7" s="14">
+        <v>3468.1826983888504</v>
+      </c>
+      <c r="AF7" s="14">
+        <v>561.03215660294541</v>
+      </c>
+      <c r="AG7" s="14">
+        <v>773.95777512524228</v>
+      </c>
+      <c r="AH7" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="15"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
-      <c r="AF8" s="14"/>
-      <c r="AG8" s="14"/>
-      <c r="AH8" s="14"/>
+      <c r="A8" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="9">
+        <v>362998</v>
+      </c>
+      <c r="E8" s="10">
+        <v>303712</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0.83667678609799501</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>50.041577086712323</v>
+      </c>
+      <c r="I8" s="14">
+        <v>127907.62999999999</v>
+      </c>
+      <c r="J8" s="14">
+        <v>326.40263292073672</v>
+      </c>
+      <c r="K8" s="9">
+        <v>17.868997681682693</v>
+      </c>
+      <c r="L8" s="9">
+        <v>223.03191851700251</v>
+      </c>
+      <c r="M8" s="14">
+        <v>78.901445527430013</v>
+      </c>
+      <c r="N8" s="12">
+        <v>2417.4945405776507</v>
+      </c>
+      <c r="O8" s="14">
+        <v>1985.6252987529826</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>27.546042002593961</v>
+      </c>
+      <c r="R8" s="14">
+        <v>0</v>
+      </c>
+      <c r="S8" s="14">
+        <v>0</v>
+      </c>
+      <c r="T8" s="14">
+        <v>197.23325370057307</v>
+      </c>
+      <c r="U8" s="14">
+        <v>225.69190805125299</v>
+      </c>
+      <c r="V8" s="14">
+        <v>1189.6141488100238</v>
+      </c>
+      <c r="W8" s="14">
+        <v>2127.4023816323338</v>
+      </c>
+      <c r="X8" s="14">
+        <v>4680.3384154287396</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>223.69062821706456</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>1243.4606726550944</v>
+      </c>
+      <c r="AA8" s="14">
+        <v>164.94809481953286</v>
+      </c>
+      <c r="AB8" s="14">
+        <v>29.956919504820988</v>
+      </c>
+      <c r="AC8" s="14">
+        <v>69.057927300503067</v>
+      </c>
+      <c r="AD8" s="14">
+        <v>997.66374690394821</v>
+      </c>
+      <c r="AE8" s="14">
+        <v>6712.8626471721382</v>
+      </c>
+      <c r="AF8" s="14">
+        <v>1085.909288940258</v>
+      </c>
+      <c r="AG8" s="14">
+        <v>1498.0387975351637</v>
+      </c>
+      <c r="AH8" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="15"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
-      <c r="AF9" s="14"/>
-      <c r="AG9" s="14"/>
-      <c r="AH9" s="14"/>
+      <c r="A9" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="9">
+        <v>445462</v>
+      </c>
+      <c r="E9" s="10">
+        <v>375812</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.84364547368799137</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
+        <v>61.921245021966641</v>
+      </c>
+      <c r="I9" s="14">
+        <v>157314.01</v>
+      </c>
+      <c r="J9" s="14">
+        <v>403.88929737121981</v>
+      </c>
+      <c r="K9" s="9">
+        <v>22.111025434452824</v>
+      </c>
+      <c r="L9" s="9">
+        <v>275.97879359956721</v>
+      </c>
+      <c r="M9" s="14">
+        <v>97.632329465264874</v>
+      </c>
+      <c r="N9" s="12">
+        <v>2991.3979634771367</v>
+      </c>
+      <c r="O9" s="14">
+        <v>2457.0047109595798</v>
+      </c>
+      <c r="P9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>34.085360924424592</v>
+      </c>
+      <c r="R9" s="14">
+        <v>0</v>
+      </c>
+      <c r="S9" s="14">
+        <v>0</v>
+      </c>
+      <c r="T9" s="14">
+        <v>244.05563013552236</v>
+      </c>
+      <c r="U9" s="14">
+        <v>279.27025388709529</v>
+      </c>
+      <c r="V9" s="14">
+        <v>1472.0237346321273</v>
+      </c>
+      <c r="W9" s="14">
+        <v>2632.4390996931656</v>
+      </c>
+      <c r="X9" s="14">
+        <v>5791.4318188912703</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>276.79387831732515</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>1538.6532053783069</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>204.10610515988265</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>37.068570991418795</v>
+      </c>
+      <c r="AC9" s="14">
+        <v>85.451999837532455</v>
+      </c>
+      <c r="AD9" s="14">
+        <v>1234.505083933024</v>
+      </c>
+      <c r="AE9" s="14">
+        <v>8306.4690797830044</v>
+      </c>
+      <c r="AF9" s="14">
+        <v>1343.6997606127393</v>
+      </c>
+      <c r="AG9" s="14">
+        <v>1853.6671470975296</v>
+      </c>
+      <c r="AH9" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="15"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="14"/>
-      <c r="AE10" s="14"/>
-      <c r="AF10" s="14"/>
-      <c r="AG10" s="14"/>
-      <c r="AH10" s="14"/>
+      <c r="A10" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="9">
+        <v>137255</v>
+      </c>
+      <c r="E10" s="10">
+        <v>106300</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0.77447087537794612</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>17.514683793585764</v>
+      </c>
+      <c r="I10" s="14">
+        <v>48124.080000000016</v>
+      </c>
+      <c r="J10" s="14">
+        <v>114.24178129107284</v>
+      </c>
+      <c r="K10" s="9">
+        <v>6.2541962568580436</v>
+      </c>
+      <c r="L10" s="9">
+        <v>78.061758963614764</v>
+      </c>
+      <c r="M10" s="14">
+        <v>27.615713766877207</v>
+      </c>
+      <c r="N10" s="12">
+        <v>846.1294570626261</v>
+      </c>
+      <c r="O10" s="14">
+        <v>694.97408484828406</v>
+      </c>
+      <c r="P10" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>9.6411872592315682</v>
+      </c>
+      <c r="R10" s="14">
+        <v>0</v>
+      </c>
+      <c r="S10" s="14">
+        <v>0</v>
+      </c>
+      <c r="T10" s="14">
+        <v>69.032158322262276</v>
+      </c>
+      <c r="U10" s="14">
+        <v>78.992762307212729</v>
+      </c>
+      <c r="V10" s="14">
+        <v>416.36808561566721</v>
+      </c>
+      <c r="W10" s="14">
+        <v>744.5964373074396</v>
+      </c>
+      <c r="X10" s="14">
+        <v>1638.130773759598</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>78.292309093726828</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>435.21451079719122</v>
+      </c>
+      <c r="AA10" s="14">
+        <v>57.732267672388119</v>
+      </c>
+      <c r="AB10" s="14">
+        <v>10.485000735441705</v>
+      </c>
+      <c r="AC10" s="14">
+        <v>24.170456458893543</v>
+      </c>
+      <c r="AD10" s="14">
+        <v>349.18493933690365</v>
+      </c>
+      <c r="AE10" s="14">
+        <v>2349.5196086898059</v>
+      </c>
+      <c r="AF10" s="14">
+        <v>380.07111149493409</v>
+      </c>
+      <c r="AG10" s="14">
+        <v>524.31752508293346</v>
+      </c>
+      <c r="AH10" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="15"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
-      <c r="AG11" s="14"/>
-      <c r="AH11" s="14"/>
+      <c r="A11" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="9">
+        <v>145289</v>
+      </c>
+      <c r="E11" s="10">
+        <v>79500</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0.54718526522998989</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <v>13.098940372437143</v>
+      </c>
+      <c r="I11" s="14">
+        <v>52424.139999999978</v>
+      </c>
+      <c r="J11" s="14">
+        <v>85.439525989090228</v>
+      </c>
+      <c r="K11" s="9">
+        <v>4.6774092419587436</v>
+      </c>
+      <c r="L11" s="9">
+        <v>58.381089723493638</v>
+      </c>
+      <c r="M11" s="14">
+        <v>20.653332497335256</v>
+      </c>
+      <c r="N11" s="12">
+        <v>632.80613204589622</v>
+      </c>
+      <c r="O11" s="14">
+        <v>519.75954605304412</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>7.2104834158881435</v>
+      </c>
+      <c r="R11" s="14">
+        <v>0</v>
+      </c>
+      <c r="S11" s="14">
+        <v>0</v>
+      </c>
+      <c r="T11" s="14">
+        <v>51.62800175559596</v>
+      </c>
+      <c r="U11" s="14">
+        <v>59.07737162204527</v>
+      </c>
+      <c r="V11" s="14">
+        <v>311.39475829205594</v>
+      </c>
+      <c r="W11" s="14">
+        <v>556.87127719606258</v>
+      </c>
+      <c r="X11" s="14">
+        <v>1225.130729199323</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>58.553514326917053</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>325.48968587372246</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>43.177001692896106</v>
+      </c>
+      <c r="AB11" s="14">
+        <v>7.8415574644178321</v>
+      </c>
+      <c r="AC11" s="14">
+        <v>18.076681923631575</v>
+      </c>
+      <c r="AD11" s="14">
+        <v>261.14960185591571</v>
+      </c>
+      <c r="AE11" s="14">
+        <v>1757.1665935168351</v>
+      </c>
+      <c r="AF11" s="14">
+        <v>284.24885572763179</v>
+      </c>
+      <c r="AG11" s="14">
+        <v>392.12834660482793</v>
+      </c>
+      <c r="AH11" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="15"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="14"/>
-      <c r="AF12" s="14"/>
-      <c r="AG12" s="14"/>
-      <c r="AH12" s="14"/>
+      <c r="A12" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="9">
+        <v>162749</v>
+      </c>
+      <c r="E12" s="10">
+        <v>118512</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0.72818880607561332</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <v>19.526812848028563</v>
+      </c>
+      <c r="I12" s="14">
+        <v>59696.94</v>
+      </c>
+      <c r="J12" s="14">
+        <v>127.36615225181208</v>
+      </c>
+      <c r="K12" s="9">
+        <v>6.9726933846920085</v>
+      </c>
+      <c r="L12" s="9">
+        <v>87.029681827807281</v>
+      </c>
+      <c r="M12" s="14">
+        <v>30.788273470744603</v>
+      </c>
+      <c r="N12" s="12">
+        <v>943.33484680532399</v>
+      </c>
+      <c r="O12" s="14">
+        <v>774.81438140677187</v>
+      </c>
+      <c r="P12" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>10.748790070235668</v>
+      </c>
+      <c r="R12" s="14">
+        <v>0</v>
+      </c>
+      <c r="S12" s="14">
+        <v>0</v>
+      </c>
+      <c r="T12" s="14">
+        <v>76.962738918983504</v>
+      </c>
+      <c r="U12" s="14">
+        <v>88.06764107763307</v>
+      </c>
+      <c r="V12" s="14">
+        <v>464.20145402148592</v>
+      </c>
+      <c r="W12" s="14">
+        <v>830.13746922087751</v>
+      </c>
+      <c r="X12" s="14">
+        <v>1826.3231821241532</v>
+      </c>
+      <c r="Y12" s="14">
+        <v>87.286718112095514</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>485.21300191530315</v>
+      </c>
+      <c r="AA12" s="14">
+        <v>64.364689617968594</v>
+      </c>
+      <c r="AB12" s="14">
+        <v>11.689542870730643</v>
+      </c>
+      <c r="AC12" s="14">
+        <v>26.947216706080823</v>
+      </c>
+      <c r="AD12" s="14">
+        <v>389.30014610249412</v>
+      </c>
+      <c r="AE12" s="14">
+        <v>2619.438079633549</v>
+      </c>
+      <c r="AF12" s="14">
+        <v>423.73459610054215</v>
+      </c>
+      <c r="AG12" s="14">
+        <v>584.55238506706121</v>
+      </c>
+      <c r="AH12" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="15"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="14"/>
+      <c r="A13" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="9">
+        <v>356089</v>
+      </c>
+      <c r="E13" s="10">
+        <v>294812</v>
+      </c>
+      <c r="F13" s="11">
+        <v>0.82791661635153013</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>48.575154831181621</v>
+      </c>
+      <c r="I13" s="14">
+        <v>129964.09000000001</v>
+      </c>
+      <c r="J13" s="14">
+        <v>316.83770485403352</v>
+      </c>
+      <c r="K13" s="9">
+        <v>17.345363187928818</v>
+      </c>
+      <c r="L13" s="9">
+        <v>216.49617388129064</v>
+      </c>
+      <c r="M13" s="14">
+        <v>76.589311449111975</v>
+      </c>
+      <c r="N13" s="12">
+        <v>2346.6520930907518</v>
+      </c>
+      <c r="O13" s="14">
+        <v>1927.4383810187426</v>
+      </c>
+      <c r="P13" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>26.738830651632895</v>
+      </c>
+      <c r="R13" s="14">
+        <v>0</v>
+      </c>
+      <c r="S13" s="14">
+        <v>0</v>
+      </c>
+      <c r="T13" s="14">
+        <v>191.45351513925479</v>
+      </c>
+      <c r="U13" s="14">
+        <v>219.07821487595484</v>
+      </c>
+      <c r="V13" s="14">
+        <v>1154.7536035421081</v>
+      </c>
+      <c r="W13" s="14">
+        <v>2065.0608172669886</v>
+      </c>
+      <c r="X13" s="14">
+        <v>4543.1854155561114</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>217.13558070122099</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>1207.0222046767783</v>
+      </c>
+      <c r="AA13" s="14">
+        <v>160.1144430576866</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>29.079059612577986</v>
+      </c>
+      <c r="AC13" s="14">
+        <v>67.034248443643676</v>
+      </c>
+      <c r="AD13" s="14">
+        <v>968.42813109869473</v>
+      </c>
+      <c r="AE13" s="14">
+        <v>6516.1483995960398</v>
+      </c>
+      <c r="AF13" s="14">
+        <v>1054.0877189279822</v>
+      </c>
+      <c r="AG13" s="14">
+        <v>1454.1401524435539</v>
+      </c>
+      <c r="AH13" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="14"/>
-      <c r="AE14" s="14"/>
-      <c r="AF14" s="14"/>
-      <c r="AG14" s="14"/>
-      <c r="AH14" s="14"/>
+      <c r="A14" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="1">
+        <v>85004</v>
+      </c>
+      <c r="E14" s="1">
+        <v>70752</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0.8323373017740342</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>11.657562631832361</v>
+      </c>
+      <c r="I14" s="14">
+        <v>29054.810000000005</v>
+      </c>
+      <c r="J14" s="14">
+        <v>76.037953997234112</v>
+      </c>
+      <c r="K14" s="9">
+        <v>4.1627177193341511</v>
+      </c>
+      <c r="L14" s="9">
+        <v>51.956966793919776</v>
+      </c>
+      <c r="M14" s="14">
+        <v>18.380686551590745</v>
+      </c>
+      <c r="N14" s="12">
+        <v>563.17357804416667</v>
+      </c>
+      <c r="O14" s="14">
+        <v>462.56638241943364</v>
+      </c>
+      <c r="P14" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>6.4170581464266405</v>
+      </c>
+      <c r="R14" s="14">
+        <v>0</v>
+      </c>
+      <c r="S14" s="14">
+        <v>0</v>
+      </c>
+      <c r="T14" s="14">
+        <v>45.946973335999061</v>
+      </c>
+      <c r="U14" s="14">
+        <v>52.576631408842097</v>
+      </c>
+      <c r="V14" s="14">
+        <v>277.12958413433387</v>
+      </c>
+      <c r="W14" s="14">
+        <v>495.59442269403542</v>
+      </c>
+      <c r="X14" s="14">
+        <v>1090.3201176391258</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>52.110418184377799</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>289.67353779795741</v>
+      </c>
+      <c r="AA14" s="14">
+        <v>38.425902185858931</v>
+      </c>
+      <c r="AB14" s="14">
+        <v>6.9786902355030245</v>
+      </c>
+      <c r="AC14" s="14">
+        <v>16.087564773091589</v>
+      </c>
+      <c r="AD14" s="14">
+        <v>232.41329094980819</v>
+      </c>
+      <c r="AE14" s="14">
+        <v>1563.8119600566429</v>
+      </c>
+      <c r="AF14" s="14">
+        <v>252.97075522567806</v>
+      </c>
+      <c r="AG14" s="14">
+        <v>348.9794311821986</v>
+      </c>
+      <c r="AH14" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
-      <c r="AF15" s="14"/>
-      <c r="AG15" s="14"/>
-      <c r="AH15" s="14"/>
+      <c r="A15" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="1">
+        <v>73465</v>
+      </c>
+      <c r="E15" s="1">
+        <v>61097</v>
+      </c>
+      <c r="F15" s="11">
+        <v>0.83164772340570337</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>10.066741634399902</v>
+      </c>
+      <c r="I15" s="14">
+        <v>25111.010000000002</v>
+      </c>
+      <c r="J15" s="14">
+        <v>65.661619111389243</v>
+      </c>
+      <c r="K15" s="9">
+        <v>3.5946625466157656</v>
+      </c>
+      <c r="L15" s="9">
+        <v>44.866785394167181</v>
+      </c>
+      <c r="M15" s="14">
+        <v>15.872410762134493</v>
+      </c>
+      <c r="N15" s="12">
+        <v>486.32146225922168</v>
+      </c>
+      <c r="O15" s="14">
+        <v>399.44338346167086</v>
+      </c>
+      <c r="P15" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>5.5413698774907907</v>
+      </c>
+      <c r="R15" s="14">
+        <v>0</v>
+      </c>
+      <c r="S15" s="14">
+        <v>0</v>
+      </c>
+      <c r="T15" s="14">
+        <v>39.676931110209388</v>
+      </c>
+      <c r="U15" s="14">
+        <v>45.401888981032698</v>
+      </c>
+      <c r="V15" s="14">
+        <v>239.31176789144328</v>
+      </c>
+      <c r="W15" s="14">
+        <v>427.96433236286583</v>
+      </c>
+      <c r="X15" s="14">
+        <v>941.53222845145967</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>44.99929641297674</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>250.14394135631224</v>
+      </c>
+      <c r="AA15" s="14">
+        <v>33.182204684665074</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>6.0263602063337895</v>
+      </c>
+      <c r="AC15" s="14">
+        <v>13.892214282869414</v>
+      </c>
+      <c r="AD15" s="14">
+        <v>200.69757515208659</v>
+      </c>
+      <c r="AE15" s="14">
+        <v>1350.4101555232462</v>
+      </c>
+      <c r="AF15" s="14">
+        <v>218.44971494831597</v>
+      </c>
+      <c r="AG15" s="14">
+        <v>301.35679990585123</v>
+      </c>
+      <c r="AH15" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="14"/>
-      <c r="AE16" s="14"/>
-      <c r="AF16" s="14"/>
-      <c r="AG16" s="14"/>
-      <c r="AH16" s="14"/>
+      <c r="A16" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="1">
+        <v>81065</v>
+      </c>
+      <c r="E16" s="1">
+        <v>68027</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0.83916610127675317</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>11.208573795167064</v>
+      </c>
+      <c r="I16" s="14">
+        <v>27708.75</v>
+      </c>
+      <c r="J16" s="14">
+        <v>73.109366471192956</v>
+      </c>
+      <c r="K16" s="9">
+        <v>4.0023914277072636</v>
+      </c>
+      <c r="L16" s="9">
+        <v>49.955853970064176</v>
+      </c>
+      <c r="M16" s="14">
+        <v>17.672757859072018</v>
+      </c>
+      <c r="N16" s="12">
+        <v>541.48305339227909</v>
+      </c>
+      <c r="O16" s="14">
+        <v>444.75072502327583</v>
+      </c>
+      <c r="P16" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>6.1699063563851917</v>
+      </c>
+      <c r="R16" s="14">
+        <v>0</v>
+      </c>
+      <c r="S16" s="14">
+        <v>0</v>
+      </c>
+      <c r="T16" s="14">
+        <v>44.177334282112284</v>
+      </c>
+      <c r="U16" s="14">
+        <v>50.551652318652494</v>
+      </c>
+      <c r="V16" s="14">
+        <v>266.45599021803383</v>
+      </c>
+      <c r="W16" s="14">
+        <v>476.5066965259943</v>
+      </c>
+      <c r="X16" s="14">
+        <v>1048.3266429590233</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>50.103395209021208</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>278.51681586077638</v>
+      </c>
+      <c r="AA16" s="14">
+        <v>36.94593577563073</v>
+      </c>
+      <c r="AB16" s="14">
+        <v>6.7099072909679478</v>
+      </c>
+      <c r="AC16" s="14">
+        <v>15.467955235457676</v>
+      </c>
+      <c r="AD16" s="14">
+        <v>223.46193667235698</v>
+      </c>
+      <c r="AE16" s="14">
+        <v>1503.5820359392419</v>
+      </c>
+      <c r="AF16" s="14">
+        <v>243.22763407023407</v>
+      </c>
+      <c r="AG16" s="14">
+        <v>335.53855389291357</v>
+      </c>
+      <c r="AH16" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="14"/>
-      <c r="AH17" s="14"/>
+      <c r="A17" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="1">
+        <v>76416</v>
+      </c>
+      <c r="E17" s="1">
+        <v>63928</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0.83657872696817426</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>10.533195724895116</v>
+      </c>
+      <c r="I17" s="14">
+        <v>26119.03</v>
+      </c>
+      <c r="J17" s="14">
+        <v>68.704126005415844</v>
+      </c>
+      <c r="K17" s="9">
+        <v>3.7612253838985983</v>
+      </c>
+      <c r="L17" s="9">
+        <v>46.945739670987436</v>
+      </c>
+      <c r="M17" s="14">
+        <v>16.60787723131633</v>
+      </c>
+      <c r="N17" s="12">
+        <v>508.85572842050385</v>
+      </c>
+      <c r="O17" s="14">
+        <v>417.95205358589942</v>
+      </c>
+      <c r="P17" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>5.798135645420091</v>
+      </c>
+      <c r="R17" s="14">
+        <v>0</v>
+      </c>
+      <c r="S17" s="14">
+        <v>0</v>
+      </c>
+      <c r="T17" s="14">
+        <v>41.515407499770298</v>
+      </c>
+      <c r="U17" s="14">
+        <v>47.505637900051696</v>
+      </c>
+      <c r="V17" s="14">
+        <v>250.40055481879938</v>
+      </c>
+      <c r="W17" s="14">
+        <v>447.79455356716835</v>
+      </c>
+      <c r="X17" s="14">
+        <v>985.15921077049461</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>47.084390740769223</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>261.73464954132493</v>
+      </c>
+      <c r="AA17" s="14">
+        <v>34.719740430483796</v>
+      </c>
+      <c r="AB17" s="14">
+        <v>6.3055985608214238</v>
+      </c>
+      <c r="AC17" s="14">
+        <v>14.535926063068169</v>
+      </c>
+      <c r="AD17" s="14">
+        <v>209.99712889867899</v>
+      </c>
+      <c r="AE17" s="14">
+        <v>1412.982968432003</v>
+      </c>
+      <c r="AF17" s="14">
+        <v>228.57183457806346</v>
+      </c>
+      <c r="AG17" s="14">
+        <v>315.3205149906093</v>
+      </c>
+      <c r="AH17" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
-      <c r="AF18" s="14"/>
-      <c r="AG18" s="14"/>
-      <c r="AH18" s="14"/>
+      <c r="A18" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1">
+        <v>21216</v>
+      </c>
+      <c r="E18" s="1">
+        <v>17544</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0.82692307692307687</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
+        <v>2.8906642753966949</v>
+      </c>
+      <c r="I18" s="14">
+        <v>7251.74</v>
+      </c>
+      <c r="J18" s="14">
+        <v>18.854730112611307</v>
+      </c>
+      <c r="K18" s="9">
+        <v>1.0322071413952729</v>
+      </c>
+      <c r="L18" s="9">
+        <v>12.883494818980784</v>
+      </c>
+      <c r="M18" s="14">
+        <v>4.5577618280911922</v>
+      </c>
+      <c r="N18" s="12">
+        <v>139.64717963035477</v>
+      </c>
+      <c r="O18" s="14">
+        <v>114.70014435163026</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="14">
+        <v>1.5912040383439192</v>
+      </c>
+      <c r="R18" s="14">
+        <v>0</v>
+      </c>
+      <c r="S18" s="14">
+        <v>0</v>
+      </c>
+      <c r="T18" s="14">
+        <v>11.393228462895289</v>
+      </c>
+      <c r="U18" s="14">
+        <v>13.037149782857385</v>
+      </c>
+      <c r="V18" s="14">
+        <v>68.718360244978982</v>
+      </c>
+      <c r="W18" s="14">
+        <v>122.88993317141788</v>
+      </c>
+      <c r="X18" s="14">
+        <v>270.36092469274121</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>12.921545350332487</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>71.828818226019962</v>
+      </c>
+      <c r="AA18" s="14">
+        <v>9.5282681471719393</v>
+      </c>
+      <c r="AB18" s="14">
+        <v>1.7304689830911502</v>
+      </c>
+      <c r="AC18" s="14">
+        <v>3.9891485241282063</v>
+      </c>
+      <c r="AD18" s="14">
+        <v>57.630297043524344</v>
+      </c>
+      <c r="AE18" s="14">
+        <v>387.77019769382838</v>
+      </c>
+      <c r="AF18" s="14">
+        <v>62.727822954535505</v>
+      </c>
+      <c r="AG18" s="14">
+        <v>86.534587582831463</v>
+      </c>
+      <c r="AH18" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="14"/>
-      <c r="AF19" s="14"/>
-      <c r="AG19" s="14"/>
-      <c r="AH19" s="14"/>
+      <c r="A19" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="1">
+        <v>16523</v>
+      </c>
+      <c r="E19" s="1">
+        <v>13567</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0.82109786358409487</v>
+      </c>
+      <c r="G19" s="13">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13">
+        <v>2.2353877236837074</v>
+      </c>
+      <c r="I19" s="14">
+        <v>5647.66</v>
+      </c>
+      <c r="J19" s="14">
+        <v>14.580604391119333</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0.79821900862458206</v>
+      </c>
+      <c r="L19" s="9">
+        <v>9.962971626146393</v>
+      </c>
+      <c r="M19" s="14">
+        <v>3.5245756225326721</v>
+      </c>
+      <c r="N19" s="12">
+        <v>107.9909533769393</v>
+      </c>
+      <c r="O19" s="14">
+        <v>88.699091337127655</v>
+      </c>
+      <c r="P19" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="14">
+        <v>1.2304984717403074</v>
+      </c>
+      <c r="R19" s="14">
+        <v>0</v>
+      </c>
+      <c r="S19" s="14">
+        <v>0</v>
+      </c>
+      <c r="T19" s="14">
+        <v>8.8105295574612619</v>
+      </c>
+      <c r="U19" s="14">
+        <v>10.081794978569663</v>
+      </c>
+      <c r="V19" s="14">
+        <v>53.140788499978903</v>
+      </c>
+      <c r="W19" s="14">
+        <v>95.032359971307926</v>
+      </c>
+      <c r="X19" s="14">
+        <v>209.07356733392726</v>
+      </c>
+      <c r="Y19" s="14">
+        <v>9.9923965896010518</v>
+      </c>
+      <c r="Z19" s="14">
+        <v>55.546145512563434</v>
+      </c>
+      <c r="AA19" s="14">
+        <v>7.3683318486480678</v>
+      </c>
+      <c r="AB19" s="14">
+        <v>1.3381938379843614</v>
+      </c>
+      <c r="AC19" s="14">
+        <v>3.084859668652951</v>
+      </c>
+      <c r="AD19" s="14">
+        <v>44.566247149424008</v>
+      </c>
+      <c r="AE19" s="14">
+        <v>299.86766256909311</v>
+      </c>
+      <c r="AF19" s="14">
+        <v>48.508229253544414</v>
+      </c>
+      <c r="AG19" s="14">
+        <v>66.918305388524544</v>
+      </c>
+      <c r="AH19" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="14"/>
-      <c r="AG20" s="14"/>
-      <c r="AH20" s="14"/>
+      <c r="A20" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="1">
+        <v>76746</v>
+      </c>
+      <c r="E20" s="1">
+        <v>64335</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0.83828473145180205</v>
+      </c>
+      <c r="G20" s="13">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13">
+        <v>10.600255708940171</v>
+      </c>
+      <c r="I20" s="14">
+        <v>26232.43</v>
+      </c>
+      <c r="J20" s="14">
+        <v>69.141533390039243</v>
+      </c>
+      <c r="K20" s="9">
+        <v>3.7851713658039721</v>
+      </c>
+      <c r="L20" s="9">
+        <v>47.244621476238535</v>
+      </c>
+      <c r="M20" s="14">
+        <v>16.713611902088854</v>
+      </c>
+      <c r="N20" s="12">
+        <v>512.09537742355644</v>
+      </c>
+      <c r="O20" s="14">
+        <v>420.61296094745398</v>
+      </c>
+      <c r="P20" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>5.8350496925932536</v>
+      </c>
+      <c r="R20" s="14">
+        <v>0</v>
+      </c>
+      <c r="S20" s="14">
+        <v>0</v>
+      </c>
+      <c r="T20" s="14">
+        <v>41.779716892405865</v>
+      </c>
+      <c r="U20" s="14">
+        <v>47.808084318292856</v>
+      </c>
+      <c r="V20" s="14">
+        <v>251.99473930464677</v>
+      </c>
+      <c r="W20" s="14">
+        <v>450.64545431960607</v>
+      </c>
+      <c r="X20" s="14">
+        <v>991.43126368601827</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>47.384155273235329</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>263.40099296460295</v>
+      </c>
+      <c r="AA20" s="14">
+        <v>34.940784954873848</v>
+      </c>
+      <c r="AB20" s="14">
+        <v>6.345743389601525</v>
+      </c>
+      <c r="AC20" s="14">
+        <v>14.62846957933129</v>
+      </c>
+      <c r="AD20" s="14">
+        <v>211.33408346415521</v>
+      </c>
+      <c r="AE20" s="14">
+        <v>1421.9787772818313</v>
+      </c>
+      <c r="AF20" s="14">
+        <v>230.02704570109677</v>
+      </c>
+      <c r="AG20" s="14">
+        <v>317.32801482794474</v>
+      </c>
+      <c r="AH20" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14"/>
-      <c r="AH21" s="14"/>
+      <c r="A21" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="1">
+        <v>41336</v>
+      </c>
+      <c r="E21" s="1">
+        <v>37137</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0.89841784401006386</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
+        <v>6.1189352026565809</v>
+      </c>
+      <c r="I21" s="14">
+        <v>12479.9</v>
+      </c>
+      <c r="J21" s="14">
+        <v>39.911543102601804</v>
+      </c>
+      <c r="K21" s="9">
+        <v>2.1849678870266902</v>
+      </c>
+      <c r="L21" s="9">
+        <v>27.271679610835012</v>
+      </c>
+      <c r="M21" s="14">
+        <v>9.6478340748872888</v>
+      </c>
+      <c r="N21" s="12">
+        <v>295.60404183381695</v>
+      </c>
+      <c r="O21" s="14">
+        <v>242.79635549398614</v>
+      </c>
+      <c r="P21" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>3.3682480832180879</v>
+      </c>
+      <c r="R21" s="14">
+        <v>0</v>
+      </c>
+      <c r="S21" s="14">
+        <v>0</v>
+      </c>
+      <c r="T21" s="14">
+        <v>24.117095612548013</v>
+      </c>
+      <c r="U21" s="14">
+        <v>27.596935219218807</v>
+      </c>
+      <c r="V21" s="14">
+        <v>145.46247973197586</v>
+      </c>
+      <c r="W21" s="14">
+        <v>260.13243548717202</v>
+      </c>
+      <c r="X21" s="14">
+        <v>572.29786025503472</v>
+      </c>
+      <c r="Y21" s="14">
+        <v>27.352224673694572</v>
+      </c>
+      <c r="Z21" s="14">
+        <v>152.04667250682306</v>
+      </c>
+      <c r="AA21" s="14">
+        <v>20.16936241344758</v>
+      </c>
+      <c r="AB21" s="14">
+        <v>3.6630430132840885</v>
+      </c>
+      <c r="AC21" s="14">
+        <v>8.4441979446277475</v>
+      </c>
+      <c r="AD21" s="14">
+        <v>121.99135552356154</v>
+      </c>
+      <c r="AE21" s="14">
+        <v>820.82887777905285</v>
+      </c>
+      <c r="AF21" s="14">
+        <v>132.78175792650393</v>
+      </c>
+      <c r="AG21" s="14">
+        <v>183.17572840079868</v>
+      </c>
+      <c r="AH21" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="14"/>
-      <c r="AF22" s="14"/>
-      <c r="AG22" s="14"/>
-      <c r="AH22" s="14"/>
+      <c r="A22" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="1">
+        <v>41331</v>
+      </c>
+      <c r="E22" s="1">
+        <v>37198</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0.9000024194914229</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <v>6.1289859619360607</v>
+      </c>
+      <c r="I22" s="14">
+        <v>12478.38</v>
+      </c>
+      <c r="J22" s="14">
+        <v>39.977100474744375</v>
+      </c>
+      <c r="K22" s="9">
+        <v>2.1885568425456774</v>
+      </c>
+      <c r="L22" s="9">
+        <v>27.316475163956181</v>
+      </c>
+      <c r="M22" s="14">
+        <v>9.6636812859858736</v>
+      </c>
+      <c r="N22" s="12">
+        <v>296.08959119299686</v>
+      </c>
+      <c r="O22" s="14">
+        <v>243.19516470542305</v>
+      </c>
+      <c r="P22" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>3.3737806553988321</v>
+      </c>
+      <c r="R22" s="14">
+        <v>0</v>
+      </c>
+      <c r="S22" s="14">
+        <v>0</v>
+      </c>
+      <c r="T22" s="14">
+        <v>24.156709551001995</v>
+      </c>
+      <c r="U22" s="14">
+        <v>27.642265026375345</v>
+      </c>
+      <c r="V22" s="14">
+        <v>145.70141155909303</v>
+      </c>
+      <c r="W22" s="14">
+        <v>260.55972036652997</v>
+      </c>
+      <c r="X22" s="14">
+        <v>573.23789766989205</v>
+      </c>
+      <c r="Y22" s="14">
+        <v>27.39715252745485</v>
+      </c>
+      <c r="Z22" s="14">
+        <v>152.29641930982049</v>
+      </c>
+      <c r="AA22" s="14">
+        <v>20.20249193675911</v>
+      </c>
+      <c r="AB22" s="14">
+        <v>3.6690598058039563</v>
+      </c>
+      <c r="AC22" s="14">
+        <v>8.458068103084873</v>
+      </c>
+      <c r="AD22" s="14">
+        <v>122.19173446335036</v>
+      </c>
+      <c r="AE22" s="14">
+        <v>822.17714397030477</v>
+      </c>
+      <c r="AF22" s="14">
+        <v>132.99986082209369</v>
+      </c>
+      <c r="AG22" s="14">
+        <v>183.47660675479736</v>
+      </c>
+      <c r="AH22" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
-      <c r="AF23" s="14"/>
-      <c r="AG23" s="14"/>
-      <c r="AH23" s="14"/>
+      <c r="A23" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="1">
+        <v>40243</v>
+      </c>
+      <c r="E23" s="1">
+        <v>36285</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0.90164749148920309</v>
+      </c>
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>5.9785541058349905</v>
+      </c>
+      <c r="I23" s="14">
+        <v>12146.75</v>
+      </c>
+      <c r="J23" s="14">
+        <v>38.995889314643257</v>
+      </c>
+      <c r="K23" s="9">
+        <v>2.1348401804336228</v>
+      </c>
+      <c r="L23" s="9">
+        <v>26.646010573798325</v>
+      </c>
+      <c r="M23" s="14">
+        <v>9.4264927001988656</v>
+      </c>
+      <c r="N23" s="12">
+        <v>288.82227045641946</v>
+      </c>
+      <c r="O23" s="14">
+        <v>237.22610224571955</v>
+      </c>
+      <c r="P23" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>3.2909734684968712</v>
+      </c>
+      <c r="R23" s="14">
+        <v>0</v>
+      </c>
+      <c r="S23" s="14">
+        <v>0</v>
+      </c>
+      <c r="T23" s="14">
+        <v>23.563799291846532</v>
+      </c>
+      <c r="U23" s="14">
+        <v>26.963804142212737</v>
+      </c>
+      <c r="V23" s="14">
+        <v>142.12526798273271</v>
+      </c>
+      <c r="W23" s="14">
+        <v>254.16445651646703</v>
+      </c>
+      <c r="X23" s="14">
+        <v>559.16815734587976</v>
+      </c>
+      <c r="Y23" s="14">
+        <v>26.724707765436293</v>
+      </c>
+      <c r="Z23" s="14">
+        <v>148.55840568462918</v>
+      </c>
+      <c r="AA23" s="14">
+        <v>19.706635300965221</v>
+      </c>
+      <c r="AB23" s="14">
+        <v>3.5790051898918369</v>
+      </c>
+      <c r="AC23" s="14">
+        <v>8.2504704855216566</v>
+      </c>
+      <c r="AD23" s="14">
+        <v>119.19262016782267</v>
+      </c>
+      <c r="AE23" s="14">
+        <v>801.99735655041968</v>
+      </c>
+      <c r="AF23" s="14">
+        <v>129.73546830285684</v>
+      </c>
+      <c r="AG23" s="14">
+        <v>178.97329630888279</v>
+      </c>
+      <c r="AH23" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="14"/>
-      <c r="AF24" s="14"/>
-      <c r="AG24" s="14"/>
-      <c r="AH24" s="14"/>
+      <c r="A24" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="1">
+        <v>41283</v>
+      </c>
+      <c r="E24" s="1">
+        <v>37198</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0.90104885788339029</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13">
+        <v>6.1289859619360607</v>
+      </c>
+      <c r="I24" s="14">
+        <v>12460.630000000001</v>
+      </c>
+      <c r="J24" s="14">
+        <v>39.977100474744375</v>
+      </c>
+      <c r="K24" s="9">
+        <v>2.1885568425456774</v>
+      </c>
+      <c r="L24" s="9">
+        <v>27.316475163956181</v>
+      </c>
+      <c r="M24" s="14">
+        <v>9.6636812859858736</v>
+      </c>
+      <c r="N24" s="12">
+        <v>296.08959119299686</v>
+      </c>
+      <c r="O24" s="14">
+        <v>243.19516470542305</v>
+      </c>
+      <c r="P24" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="14">
+        <v>3.3737806553988321</v>
+      </c>
+      <c r="R24" s="14">
+        <v>0</v>
+      </c>
+      <c r="S24" s="14">
+        <v>0</v>
+      </c>
+      <c r="T24" s="14">
+        <v>24.156709551001995</v>
+      </c>
+      <c r="U24" s="14">
+        <v>27.642265026375345</v>
+      </c>
+      <c r="V24" s="14">
+        <v>145.70141155909303</v>
+      </c>
+      <c r="W24" s="14">
+        <v>260.55972036652997</v>
+      </c>
+      <c r="X24" s="14">
+        <v>573.23789766989205</v>
+      </c>
+      <c r="Y24" s="14">
+        <v>27.39715252745485</v>
+      </c>
+      <c r="Z24" s="14">
+        <v>152.29641930982049</v>
+      </c>
+      <c r="AA24" s="14">
+        <v>20.20249193675911</v>
+      </c>
+      <c r="AB24" s="14">
+        <v>3.6690598058039563</v>
+      </c>
+      <c r="AC24" s="14">
+        <v>8.458068103084873</v>
+      </c>
+      <c r="AD24" s="14">
+        <v>122.19173446335036</v>
+      </c>
+      <c r="AE24" s="14">
+        <v>822.17714397030477</v>
+      </c>
+      <c r="AF24" s="14">
+        <v>132.99986082209369</v>
+      </c>
+      <c r="AG24" s="14">
+        <v>183.47660675479736</v>
+      </c>
+      <c r="AH24" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="14"/>
-      <c r="AF25" s="14"/>
-      <c r="AG25" s="14"/>
-      <c r="AH25" s="14"/>
+      <c r="A25" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="1">
+        <v>40937</v>
+      </c>
+      <c r="E25" s="1">
+        <v>36773</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0.89828272711727775</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
+        <v>6.058960180070831</v>
+      </c>
+      <c r="I25" s="14">
+        <v>12357.669999999998</v>
+      </c>
+      <c r="J25" s="14">
+        <v>39.520348291783833</v>
+      </c>
+      <c r="K25" s="9">
+        <v>2.1635518245855208</v>
+      </c>
+      <c r="L25" s="9">
+        <v>27.004374998767695</v>
+      </c>
+      <c r="M25" s="14">
+        <v>9.5532703889875403</v>
+      </c>
+      <c r="N25" s="12">
+        <v>292.70666532985842</v>
+      </c>
+      <c r="O25" s="14">
+        <v>240.41657593721496</v>
+      </c>
+      <c r="P25" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="14">
+        <v>3.3352340459428262</v>
+      </c>
+      <c r="R25" s="14">
+        <v>0</v>
+      </c>
+      <c r="S25" s="14">
+        <v>0</v>
+      </c>
+      <c r="T25" s="14">
+        <v>23.880710799478369</v>
+      </c>
+      <c r="U25" s="14">
+        <v>27.32644259946504</v>
+      </c>
+      <c r="V25" s="14">
+        <v>144.0367225996701</v>
+      </c>
+      <c r="W25" s="14">
+        <v>257.58273555133093</v>
+      </c>
+      <c r="X25" s="14">
+        <v>566.6884566647384</v>
+      </c>
+      <c r="Y25" s="14">
+        <v>27.084130595518499</v>
+      </c>
+      <c r="Z25" s="14">
+        <v>150.55638010860878</v>
+      </c>
+      <c r="AA25" s="14">
+        <v>19.971671487457463</v>
+      </c>
+      <c r="AB25" s="14">
+        <v>3.6271395300507789</v>
+      </c>
+      <c r="AC25" s="14">
+        <v>8.3614317531786657</v>
+      </c>
+      <c r="AD25" s="14">
+        <v>120.7956516861332</v>
+      </c>
+      <c r="AE25" s="14">
+        <v>812.78348608043495</v>
+      </c>
+      <c r="AF25" s="14">
+        <v>131.48029146757489</v>
+      </c>
+      <c r="AG25" s="14">
+        <v>181.38032314087218</v>
+      </c>
+      <c r="AH25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
-      <c r="AD26" s="14"/>
-      <c r="AE26" s="14"/>
-      <c r="AF26" s="14"/>
-      <c r="AG26" s="14"/>
-      <c r="AH26" s="14"/>
+      <c r="A26" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="1">
+        <v>41313</v>
+      </c>
+      <c r="E26" s="1">
+        <v>37162</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0.89952315251857773</v>
+      </c>
+      <c r="G26" s="13">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13">
+        <v>6.1230543662957126</v>
+      </c>
+      <c r="I26" s="14">
+        <v>12464.86</v>
+      </c>
+      <c r="J26" s="14">
+        <v>39.938410878070073</v>
+      </c>
+      <c r="K26" s="9">
+        <v>2.1864387704361112</v>
+      </c>
+      <c r="L26" s="9">
+        <v>27.290038444081393</v>
+      </c>
+      <c r="M26" s="14">
+        <v>9.6543288335342492</v>
+      </c>
+      <c r="N26" s="12">
+        <v>295.80303747282511</v>
+      </c>
+      <c r="O26" s="14">
+        <v>242.95980189211602</v>
+      </c>
+      <c r="P26" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="14">
+        <v>3.3705155308331469</v>
+      </c>
+      <c r="R26" s="14">
+        <v>0</v>
+      </c>
+      <c r="S26" s="14">
+        <v>0</v>
+      </c>
+      <c r="T26" s="14">
+        <v>24.133330833225873</v>
+      </c>
+      <c r="U26" s="14">
+        <v>27.615513009037059</v>
+      </c>
+      <c r="V26" s="14">
+        <v>145.56040261194192</v>
+      </c>
+      <c r="W26" s="14">
+        <v>260.30755224100727</v>
+      </c>
+      <c r="X26" s="14">
+        <v>572.68312149063195</v>
+      </c>
+      <c r="Y26" s="14">
+        <v>27.370637728514357</v>
+      </c>
+      <c r="Z26" s="14">
+        <v>152.14902775395313</v>
+      </c>
+      <c r="AA26" s="14">
+        <v>20.182940086935911</v>
+      </c>
+      <c r="AB26" s="14">
+        <v>3.6655089118578048</v>
+      </c>
+      <c r="AC26" s="14">
+        <v>8.4498824357987008</v>
+      </c>
+      <c r="AD26" s="14">
+        <v>122.07347803986843</v>
+      </c>
+      <c r="AE26" s="14">
+        <v>821.3814458902217</v>
+      </c>
+      <c r="AF26" s="14">
+        <v>132.8711443591227</v>
+      </c>
+      <c r="AG26" s="14">
+        <v>183.2990392016178</v>
+      </c>
+      <c r="AH26" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
-      <c r="AB27" s="14"/>
-      <c r="AC27" s="14"/>
-      <c r="AD27" s="14"/>
-      <c r="AE27" s="14"/>
-      <c r="AF27" s="14"/>
-      <c r="AG27" s="14"/>
-      <c r="AH27" s="14"/>
+      <c r="A27" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="1">
+        <v>40962</v>
+      </c>
+      <c r="E27" s="1">
+        <v>36747</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0.8970997509887213</v>
+      </c>
+      <c r="G27" s="13">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13">
+        <v>6.0546762498861346</v>
+      </c>
+      <c r="I27" s="14">
+        <v>12360.509999999998</v>
+      </c>
+      <c r="J27" s="14">
+        <v>39.492405805296833</v>
+      </c>
+      <c r="K27" s="9">
+        <v>2.1620221058397227</v>
+      </c>
+      <c r="L27" s="9">
+        <v>26.985281812191456</v>
+      </c>
+      <c r="M27" s="14">
+        <v>9.5465158399947008</v>
+      </c>
+      <c r="N27" s="12">
+        <v>292.49970986528996</v>
+      </c>
+      <c r="O27" s="14">
+        <v>240.24659168315989</v>
+      </c>
+      <c r="P27" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="14">
+        <v>3.3328759004231649</v>
+      </c>
+      <c r="R27" s="14">
+        <v>0</v>
+      </c>
+      <c r="S27" s="14">
+        <v>0</v>
+      </c>
+      <c r="T27" s="14">
+        <v>23.863826169973393</v>
+      </c>
+      <c r="U27" s="14">
+        <v>27.307121698054058</v>
+      </c>
+      <c r="V27" s="14">
+        <v>143.93488280450541</v>
+      </c>
+      <c r="W27" s="14">
+        <v>257.40061412734224</v>
+      </c>
+      <c r="X27" s="14">
+        <v>566.28778497971734</v>
+      </c>
+      <c r="Y27" s="14">
+        <v>27.064981018505922</v>
+      </c>
+      <c r="Z27" s="14">
+        <v>150.44993065159346</v>
+      </c>
+      <c r="AA27" s="14">
+        <v>19.957550707029597</v>
+      </c>
+      <c r="AB27" s="14">
+        <v>3.6245749955341142</v>
+      </c>
+      <c r="AC27" s="14">
+        <v>8.3555198823608752</v>
+      </c>
+      <c r="AD27" s="14">
+        <v>120.71024426917403</v>
+      </c>
+      <c r="AE27" s="14">
+        <v>812.20881524481933</v>
+      </c>
+      <c r="AF27" s="14">
+        <v>131.3873295776514</v>
+      </c>
+      <c r="AG27" s="14">
+        <v>181.25207990802028</v>
+      </c>
+      <c r="AH27" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="14"/>
-      <c r="AE28" s="14"/>
-      <c r="AF28" s="14"/>
-      <c r="AG28" s="14"/>
-      <c r="AH28" s="14"/>
+      <c r="A28" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="1">
+        <v>53373</v>
+      </c>
+      <c r="E28" s="1">
+        <v>44045</v>
+      </c>
+      <c r="F28" s="11">
+        <v>0.82522998519850865</v>
+      </c>
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13">
+        <v>7.2571424994213078</v>
+      </c>
+      <c r="I28" s="14">
+        <v>18244.180000000004</v>
+      </c>
+      <c r="J28" s="14">
+        <v>47.335646819993443</v>
+      </c>
+      <c r="K28" s="9">
+        <v>2.5914023907178976</v>
+      </c>
+      <c r="L28" s="9">
+        <v>32.344592413475191</v>
+      </c>
+      <c r="M28" s="14">
+        <v>11.442465784215489</v>
+      </c>
+      <c r="N28" s="12">
+        <v>350.59051680454718</v>
+      </c>
+      <c r="O28" s="14">
+        <v>287.9598642252368</v>
+      </c>
+      <c r="P28" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="14">
+        <v>3.9947892082112362</v>
+      </c>
+      <c r="R28" s="14">
+        <v>0</v>
+      </c>
+      <c r="S28" s="14">
+        <v>0</v>
+      </c>
+      <c r="T28" s="14">
+        <v>28.603211790254392</v>
+      </c>
+      <c r="U28" s="14">
+        <v>32.730350101798535</v>
+      </c>
+      <c r="V28" s="14">
+        <v>172.52052992419627</v>
+      </c>
+      <c r="W28" s="14">
+        <v>308.52069690692548</v>
+      </c>
+      <c r="X28" s="14">
+        <v>678.7532448752728</v>
+      </c>
+      <c r="Y28" s="14">
+        <v>32.440119981497631</v>
+      </c>
+      <c r="Z28" s="14">
+        <v>180.32947439381266</v>
+      </c>
+      <c r="AA28" s="14">
+        <v>23.921145151743506</v>
+      </c>
+      <c r="AB28" s="14">
+        <v>4.3444201071733763</v>
+      </c>
+      <c r="AC28" s="14">
+        <v>10.01493654498557</v>
+      </c>
+      <c r="AD28" s="14">
+        <v>144.68344922948185</v>
+      </c>
+      <c r="AE28" s="14">
+        <v>973.51449825722011</v>
+      </c>
+      <c r="AF28" s="14">
+        <v>157.48101698771751</v>
+      </c>
+      <c r="AG28" s="14">
+        <v>217.24896888314021</v>
+      </c>
+      <c r="AH28" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="14"/>
-      <c r="AC29" s="14"/>
-      <c r="AD29" s="14"/>
-      <c r="AE29" s="14"/>
-      <c r="AF29" s="14"/>
-      <c r="AG29" s="14"/>
-      <c r="AH29" s="14"/>
+      <c r="A29" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="1">
+        <v>17183</v>
+      </c>
+      <c r="E29" s="1">
+        <v>13547</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0.78839550718733631</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
+        <v>2.2320923927724023</v>
+      </c>
+      <c r="I29" s="14">
+        <v>5873.24</v>
+      </c>
+      <c r="J29" s="14">
+        <v>14.55911017074472</v>
+      </c>
+      <c r="K29" s="9">
+        <v>0.79704230189704528</v>
+      </c>
+      <c r="L29" s="9">
+        <v>9.9482845595492879</v>
+      </c>
+      <c r="M29" s="14">
+        <v>3.5193798156151037</v>
+      </c>
+      <c r="N29" s="12">
+        <v>107.83175686573279</v>
+      </c>
+      <c r="O29" s="14">
+        <v>88.568334218623747</v>
+      </c>
+      <c r="P29" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="14">
+        <v>1.22868451364826</v>
+      </c>
+      <c r="R29" s="14">
+        <v>0</v>
+      </c>
+      <c r="S29" s="14">
+        <v>0</v>
+      </c>
+      <c r="T29" s="14">
+        <v>8.7975413809189735</v>
+      </c>
+      <c r="U29" s="14">
+        <v>10.066932746715059</v>
+      </c>
+      <c r="V29" s="14">
+        <v>53.062450196006061</v>
+      </c>
+      <c r="W29" s="14">
+        <v>94.892266568239734</v>
+      </c>
+      <c r="X29" s="14">
+        <v>208.76535834544941</v>
+      </c>
+      <c r="Y29" s="14">
+        <v>9.9776661457452231</v>
+      </c>
+      <c r="Z29" s="14">
+        <v>55.46426131485935</v>
+      </c>
+      <c r="AA29" s="14">
+        <v>7.3574697098574022</v>
+      </c>
+      <c r="AB29" s="14">
+        <v>1.3362211191253883</v>
+      </c>
+      <c r="AC29" s="14">
+        <v>3.0803120757161881</v>
+      </c>
+      <c r="AD29" s="14">
+        <v>44.500549136378496</v>
+      </c>
+      <c r="AE29" s="14">
+        <v>299.42560808015804</v>
+      </c>
+      <c r="AF29" s="14">
+        <v>48.43672010744941</v>
+      </c>
+      <c r="AG29" s="14">
+        <v>66.819656747869232</v>
+      </c>
+      <c r="AH29" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
-      <c r="AD30" s="14"/>
-      <c r="AE30" s="14"/>
-      <c r="AF30" s="14"/>
-      <c r="AG30" s="14"/>
-      <c r="AH30" s="14"/>
+      <c r="A30" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="1">
+        <v>54510</v>
+      </c>
+      <c r="E30" s="1">
+        <v>45091</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0.82720601724454224</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
+        <v>7.4294883060825567</v>
+      </c>
+      <c r="I30" s="14">
+        <v>18633.189999999999</v>
+      </c>
+      <c r="J30" s="14">
+        <v>48.459794545585751</v>
+      </c>
+      <c r="K30" s="9">
+        <v>2.6529441525680717</v>
+      </c>
+      <c r="L30" s="9">
+        <v>33.112725996503798</v>
+      </c>
+      <c r="M30" s="14">
+        <v>11.714206486004327</v>
+      </c>
+      <c r="N30" s="12">
+        <v>358.91649434064789</v>
+      </c>
+      <c r="O30" s="14">
+        <v>294.79846152299132</v>
+      </c>
+      <c r="P30" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="14">
+        <v>4.0896592164253116</v>
+      </c>
+      <c r="R30" s="14">
+        <v>0</v>
+      </c>
+      <c r="S30" s="14">
+        <v>0</v>
+      </c>
+      <c r="T30" s="14">
+        <v>29.282493423416067</v>
+      </c>
+      <c r="U30" s="14">
+        <v>33.507644827794252</v>
+      </c>
+      <c r="V30" s="14">
+        <v>176.61762322197603</v>
+      </c>
+      <c r="W30" s="14">
+        <v>315.84758188739187</v>
+      </c>
+      <c r="X30" s="14">
+        <v>694.87257497266262</v>
+      </c>
+      <c r="Y30" s="14">
+        <v>33.210522195157445</v>
+      </c>
+      <c r="Z30" s="14">
+        <v>184.6120179337361</v>
+      </c>
+      <c r="AA30" s="14">
+        <v>24.489235010495321</v>
+      </c>
+      <c r="AB30" s="14">
+        <v>4.4475933034976665</v>
+      </c>
+      <c r="AC30" s="14">
+        <v>10.252775655578256</v>
+      </c>
+      <c r="AD30" s="14">
+        <v>148.11945531176221</v>
+      </c>
+      <c r="AE30" s="14">
+        <v>996.63394802852338</v>
+      </c>
+      <c r="AF30" s="14">
+        <v>161.22094532848612</v>
+      </c>
+      <c r="AG30" s="14">
+        <v>222.40829278941254</v>
+      </c>
+      <c r="AH30" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14"/>
-      <c r="AD31" s="14"/>
-      <c r="AE31" s="14"/>
-      <c r="AF31" s="14"/>
-      <c r="AG31" s="14"/>
-      <c r="AH31" s="14"/>
+      <c r="A31" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="1">
+        <v>19366</v>
+      </c>
+      <c r="E31" s="1">
+        <v>15069</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0.7781162862749148</v>
+      </c>
+      <c r="G31" s="13">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
+        <v>2.4828670751227082</v>
+      </c>
+      <c r="I31" s="14">
+        <v>6619.41</v>
+      </c>
+      <c r="J31" s="14">
+        <v>16.194820341252836</v>
+      </c>
+      <c r="K31" s="9">
+        <v>0.88658968386259507</v>
+      </c>
+      <c r="L31" s="9">
+        <v>11.065970327589001</v>
+      </c>
+      <c r="M31" s="14">
+        <v>3.9147807220420754</v>
+      </c>
+      <c r="N31" s="12">
+        <v>119.94661136854856</v>
+      </c>
+      <c r="O31" s="14">
+        <v>98.518950936771333</v>
+      </c>
+      <c r="P31" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="14">
+        <v>1.3667267244530621</v>
+      </c>
+      <c r="R31" s="14">
+        <v>0</v>
+      </c>
+      <c r="S31" s="14">
+        <v>0</v>
+      </c>
+      <c r="T31" s="14">
+        <v>9.7859416157871131</v>
+      </c>
+      <c r="U31" s="14">
+        <v>11.197948590850316</v>
+      </c>
+      <c r="V31" s="14">
+        <v>59.023995128339507</v>
+      </c>
+      <c r="W31" s="14">
+        <v>105.55337454172914</v>
+      </c>
+      <c r="X31" s="14">
+        <v>232.22006236861131</v>
+      </c>
+      <c r="Y31" s="14">
+        <v>11.098652923173749</v>
+      </c>
+      <c r="Z31" s="14">
+        <v>61.695648760139925</v>
+      </c>
+      <c r="AA31" s="14">
+        <v>8.1840784718270605</v>
+      </c>
+      <c r="AB31" s="14">
+        <v>1.4863450242932366</v>
+      </c>
+      <c r="AC31" s="14">
+        <v>3.4263838982038268</v>
+      </c>
+      <c r="AD31" s="14">
+        <v>49.500167929142066</v>
+      </c>
+      <c r="AE31" s="14">
+        <v>333.0659546881156</v>
+      </c>
+      <c r="AF31" s="14">
+        <v>53.878566125279043</v>
+      </c>
+      <c r="AG31" s="14">
+        <v>74.326818301737759</v>
+      </c>
+      <c r="AH31" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>56358</v>
+      </c>
+      <c r="E32" s="1">
+        <v>45282</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.80347066964760994</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>7.4609587162855187</v>
+      </c>
+      <c r="I32" s="1">
+        <v>19264.899999999998</v>
+      </c>
+      <c r="J32" s="1">
+        <v>48.665064350163313</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2.6641817018160481</v>
+      </c>
+      <c r="L32" s="1">
+        <v>33.25298748250615</v>
+      </c>
+      <c r="M32" s="1">
+        <v>11.763826442067108</v>
+      </c>
+      <c r="N32" s="1">
+        <v>360.43682102267013</v>
+      </c>
+      <c r="O32" s="1">
+        <v>296.04719200470367</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>4.1069825162043632</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="1">
+        <v>29.406530509394923</v>
+      </c>
+      <c r="U32" s="1">
+        <v>33.649579142005706</v>
+      </c>
+      <c r="V32" s="1">
+        <v>177.3657540249167</v>
+      </c>
+      <c r="W32" s="1">
+        <v>317.1854738866931</v>
+      </c>
+      <c r="X32" s="1">
+        <v>697.81597081262578</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>33.3511979339806</v>
+      </c>
+      <c r="Z32" s="1">
+        <v>185.39401202181008</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>24.59296843594618</v>
+      </c>
+      <c r="AB32" s="1">
+        <v>4.4664327686008587</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>10.29620516812434</v>
+      </c>
+      <c r="AD32" s="1">
+        <v>148.74687133634686</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>1000.8555683978532</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>161.90385767369338</v>
+      </c>
+      <c r="AG32" s="1">
+        <v>223.35038730767067</v>
+      </c>
+      <c r="AH32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="1">
+        <v>16456</v>
+      </c>
+      <c r="E33" s="1">
+        <v>12692</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.7712688381137579</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2.0912169963141158</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5624.75</v>
+      </c>
+      <c r="J33" s="1">
+        <v>13.640232249729976</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0.74673808929484753</v>
+      </c>
+      <c r="L33" s="1">
+        <v>9.3204124625230342</v>
+      </c>
+      <c r="M33" s="1">
+        <v>3.2972590698890452</v>
+      </c>
+      <c r="N33" s="1">
+        <v>101.02610601165428</v>
+      </c>
+      <c r="O33" s="1">
+        <v>82.978467402581572</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>1.1511378052132366</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="1">
+        <v>8.24229683373615</v>
+      </c>
+      <c r="U33" s="1">
+        <v>9.4315723349307987</v>
+      </c>
+      <c r="V33" s="1">
+        <v>49.713487701166969</v>
+      </c>
+      <c r="W33" s="1">
+        <v>88.903273587074537</v>
+      </c>
+      <c r="X33" s="1">
+        <v>195.58942408802275</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>9.347939670908568</v>
+      </c>
+      <c r="Z33" s="1">
+        <v>51.963711863009884</v>
+      </c>
+      <c r="AA33" s="1">
+        <v>6.893113276556444</v>
+      </c>
+      <c r="AB33" s="1">
+        <v>1.2518873879042909</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>2.8859024776695845</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>41.6919590786828</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>280.52777867818452</v>
+      </c>
+      <c r="AF33" s="1">
+        <v>45.379704111888088</v>
+      </c>
+      <c r="AG33" s="1">
+        <v>62.602427359855049</v>
+      </c>
+      <c r="AH33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="1">
+        <v>50996</v>
+      </c>
+      <c r="E34" s="1">
+        <v>40853</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0.80110204721938971</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>6.7312076859770391</v>
+      </c>
+      <c r="I34" s="1">
+        <v>17432.47</v>
+      </c>
+      <c r="J34" s="1">
+        <v>43.90516924820507</v>
+      </c>
+      <c r="K34" s="1">
+        <v>2.4035999970030257</v>
+      </c>
+      <c r="L34" s="1">
+        <v>30.00053658457718</v>
+      </c>
+      <c r="M34" s="1">
+        <v>10.613215000171538</v>
+      </c>
+      <c r="N34" s="1">
+        <v>325.18275361598739</v>
+      </c>
+      <c r="O34" s="1">
+        <v>267.09102811201268</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>3.7052814967204819</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="1">
+        <v>26.53029881410518</v>
+      </c>
+      <c r="U34" s="1">
+        <v>30.358337897803967</v>
+      </c>
+      <c r="V34" s="1">
+        <v>160.01773661013033</v>
+      </c>
+      <c r="W34" s="1">
+        <v>286.16178977724206</v>
+      </c>
+      <c r="X34" s="1">
+        <v>629.56309031421313</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>30.089141142107451</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>167.26075644024132</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>22.187547800753265</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>4.0295741772812788</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>9.2891407122782486</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>134.19804634741791</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>902.96260182318565</v>
+      </c>
+      <c r="AF34" s="1">
+        <v>146.06815727095525</v>
+      </c>
+      <c r="AG34" s="1">
+        <v>201.50464583455391</v>
+      </c>
+      <c r="AH34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="1">
+        <v>18641</v>
+      </c>
+      <c r="E35" s="1">
+        <v>14371</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.77093503567405186</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2.3678600263181657</v>
+      </c>
+      <c r="I35" s="1">
+        <v>6371.59</v>
+      </c>
+      <c r="J35" s="1">
+        <v>15.444672050178813</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.84552261907156112</v>
+      </c>
+      <c r="L35" s="1">
+        <v>10.553391703350027</v>
+      </c>
+      <c r="M35" s="1">
+        <v>3.7334470606189307</v>
+      </c>
+      <c r="N35" s="1">
+        <v>114.3906531274412</v>
+      </c>
+      <c r="O35" s="1">
+        <v>93.955527500984857</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>1.3034195870406102</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1">
+        <v>0</v>
+      </c>
+      <c r="T35" s="1">
+        <v>9.3326542544612519</v>
+      </c>
+      <c r="U35" s="1">
+        <v>10.679256699124686</v>
+      </c>
+      <c r="V35" s="1">
+        <v>56.289988319687239</v>
+      </c>
+      <c r="W35" s="1">
+        <v>100.66411477464924</v>
+      </c>
+      <c r="X35" s="1">
+        <v>221.4635686707355</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>10.584560432605345</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>58.837890260267493</v>
+      </c>
+      <c r="AA35" s="1">
+        <v>7.8049898280328289</v>
+      </c>
+      <c r="AB35" s="1">
+        <v>1.4174971361150774</v>
+      </c>
+      <c r="AC35" s="1">
+        <v>3.26767290471081</v>
+      </c>
+      <c r="AD35" s="1">
+        <v>47.207307273853644</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>317.63825302428222</v>
+      </c>
+      <c r="AF35" s="1">
+        <v>51.382896926563483</v>
+      </c>
+      <c r="AG35" s="1">
+        <v>70.883980742867706</v>
+      </c>
+      <c r="AH35" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2209,11 +4519,7 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
